--- a/Compititor's_Price/IKO_Prices/IKO_Prices_09-07-2026.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_09-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\IKO_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E304C7F-BD2B-4592-B2D4-15208A3AB9B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09766ACA-87F5-4166-8869-2AF3328A8561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6255" yWindow="1785" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4485" yWindow="1785" windowWidth="21600" windowHeight="11070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
